--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed approximately 150 yards from bridge. Diversion via Abbey Road parallel to river.</t>
+          <t>Towpath closed 150 yards upstream from bridge, diversion via Abbey Road and Botley Road</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.749</v>
+        <v>51.7453</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.271</v>
+        <v>-1.2631</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -572,7 +572,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed on safety grounds. 3-mile diversion via A4155 or train option available (30-minute intervals).</t>
+          <t>Footbridge closed for safety reasons, 2.7 mile diversion via Mill Lane and Harpsden</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -586,7 +586,7 @@
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.538</v>
+        <v>51.4708</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.903</v>
+        <v>-0.7196</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -619,7 +619,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5.</t>
+          <t>Unsafe footbridge north of Sandford Lock closed, diversion via NCN 5</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -633,19 +633,19 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://x.com/ThamesPathNT/status/1915740715797119304</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.743</v>
+        <v>51.7343</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.235</v>
+        <v>-1.2178</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -661,12 +661,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway closure</t>
+          <t>Abingdon Weir walkway intermittent closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway closed due to corrosion, rerouted via Abingdon town centre. May reopen if river levels are low.</t>
+          <t>Walkway closed due to corrosion when river levels high, re-routed via town centre, intermittently accessible</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -674,13 +674,13 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>active intermittent</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.672</v>
+        <v>51.6701</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.278</v>
+        <v>-1.2912</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -708,12 +708,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure near Marlow</t>
+          <t>Temple Footbridge closure Marlow</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bridge deemed unsafe and closed. Diversion via Bisham Abbey or Hambledon Lock crossing.</t>
+          <t>Closed May 2023 due to structural damage, central span removed Nov 2025, unlikely to reopen until 2028 at earliest, divert via Marlow Bridge</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -724,22 +724,26 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/temple-footbridge-update</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.51</v>
+        <v>51.5362</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.899</v>
+        <v>-0.8062</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -755,12 +759,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Runnymede Bridge 142 closure Egham</t>
+          <t>Bridge 142 closure Runnymede Egham</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Footbridge structurally damaged. Closure expected until 2026 due to funding restraints. Diversion via A308.</t>
+          <t>Cast iron bridge closed Feb 2024 due to tree strike and cracks, diversion via A308, expected until 2027</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -771,22 +775,26 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.435</v>
+        <v>51.4228</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.616</v>
+        <v>-0.5512</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -802,12 +810,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion Runnymede</t>
+          <t>Bell Weir Lock refurbishment Runnymede</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Temporary diversion around construction compound at Runnymede Pleasure Grounds for Bell Weir refurbishment (spring 2026 to autumn 2027).</t>
+          <t>Temporary diversion around construction compound for £22m weir refurbishment, works spring 2026 to autumn 2027</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -821,19 +829,19 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.437</v>
+        <v>51.422</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.612</v>
+        <v>-0.5472</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -854,7 +862,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Path section south of Streatley closed due to frequent flooding. Diversion via Manor Road and Footpath 227.</t>
+          <t>Half mile diversion due to eroding towpath, reopening unlikely until late 2026</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -868,30 +876,30 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.409</v>
+        <v>51.5238</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.124</v>
+        <v>-1.2945</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -901,7 +909,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>No access to island due to diseased trees. Thames Path unaffected.</t>
+          <t>Island closed to public due to diseased trees (ash dieback), Thames Path unaffected but island inaccessible</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -915,19 +923,19 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.437</v>
+        <v>51.4196</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.588</v>
+        <v>-0.5308</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -948,7 +956,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed since March 2024 due to structural and safety concerns.</t>
+          <t>Bridge between Rushey and Shifford locks closed March 2024 for structural safety concerns</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -966,7 +974,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -975,21 +983,21 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.616</v>
+        <v>51.8236</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.507</v>
+        <v>-1.5731</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -999,7 +1007,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank between River Brent bridge and Brentford Marina. Partial reopening with alternative routes available.</t>
+          <t>Path blocked on left bank of Grand Union Canal, partial reopening with partial route available, redevelopment ongoing</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1007,13 +1015,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>active partial</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1022,61 +1030,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.494</v>
+        <v>51.4874</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.313</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>closure</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Benson Weir closure</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Walkway closed due to safety concerns. Diversion via minor roads through Preston Crowmarsh and Howbery Business Park, crossing at Wallingford Bridge. REOPENED 2026-04-01.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>reopened</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>51.458</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>-1.148</v>
+        <v>-0.3056</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge diversion Oxford</t>
+          <t>Osney Bridge access closure Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed 150 yards upstream from bridge, diversion via Abbey Road and Botley Road</t>
+          <t>Access ramp at Botley Road/Osney Bridge closed due to water works. Diversion via Abbey Road in place.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -536,22 +536,26 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/diversion-via-abbey-road-due-to-closure-of-access-at-osney-bridge-botley-road-july-2025/</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.7453</v>
+        <v>51.754</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.2631</v>
+        <v>-1.254</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -572,7 +576,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety reasons, 2.7 mile diversion via Mill Lane and Harpsden</t>
+          <t>Footbridge closed for safety. 3-mile diversion via A4155 between Henley and Shiplake. Order initially until 31 Jan 2026, may be extended.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -583,10 +587,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,10 +603,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.4708</v>
+        <v>51.526</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.7196</v>
+        <v>-0.768</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -619,7 +627,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed, diversion via NCN 5</t>
+          <t>Unsafe footbridge north of Sandford Lock closed by Environment Agency. Diversion via NCN 5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -630,10 +638,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -642,10 +654,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.7343</v>
+        <v>51.745</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.2178</v>
+        <v>-1.308</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -661,12 +673,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway intermittent closure</t>
+          <t>Abingdon Weir walkway closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway closed due to corrosion when river levels high, re-routed via town centre, intermittently accessible</t>
+          <t>Walkway across weir closed due to corrosion. Rerouted via Abingdon town centre. May reopen at low river levels.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -674,13 +686,13 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active intermittent</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -689,10 +701,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.6701</v>
+        <v>51.666</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.2912</v>
+        <v>-1.293</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -708,12 +720,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure Marlow</t>
+          <t>Temple Footbridge closure near Marlow</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Closed May 2023 due to structural damage, central span removed Nov 2025, unlikely to reopen until 2028 at earliest, divert via Marlow Bridge</t>
+          <t>Footbridge closed due to structural damage. Diversion via Marlow Bridge and Bisham Abbey.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -731,19 +743,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/temple-footbridge-update</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.5362</v>
+        <v>51.533</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.8062</v>
+        <v>-0.8159999999999999</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -759,12 +771,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 closure Runnymede Egham</t>
+          <t>Bridge 142 closure near Runnymede M25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Cast iron bridge closed Feb 2024 due to tree strike and cracks, diversion via A308, expected until 2027</t>
+          <t>Cast iron bridge closed due to structural cracks. Diversion via A308. Expected closure until 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -782,19 +794,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.4228</v>
+        <v>51.425</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5512</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -810,12 +822,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock refurbishment Runnymede</t>
+          <t>Bell Weir refurbishment works</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Temporary diversion around construction compound for £22m weir refurbishment, works spring 2026 to autumn 2027</t>
+          <t>Small diversion around compound at Runnymede Pleasure Grounds. Bell Weir Lock remains operational. Refurbishment 2026-2027.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -826,28 +838,32 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
+          <t>https://www.gov.uk/government/publications/bell-weir-refurbishment-works-2026-lock-closure-notice/bell-weir-weir-refurbishment-works-2026-lock-closure-notice</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.422</v>
+        <v>51.427</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.5472</v>
+        <v>-0.508</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -862,7 +878,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Half mile diversion due to eroding towpath, reopening unlikely until late 2026</t>
+          <t>Half-mile towpath closure due to erosion. Diversion via Manor Road and Footpath 227. Unlikely to reopen until late 2026.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -876,19 +892,19 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.5238</v>
+        <v>51.613</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.2945</v>
+        <v>-1.155</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -909,7 +925,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island closed to public due to diseased trees (ash dieback), Thames Path unaffected but island inaccessible</t>
+          <t>No access to island due to diseased trees. Thames Path unaffected.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -923,19 +939,19 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.4196</v>
+        <v>51.431</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.5308</v>
+        <v>-0.501</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -946,7 +962,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -956,7 +972,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bridge between Rushey and Shifford locks closed March 2024 for structural safety concerns</t>
+          <t>Bridge closed March 2024 due to structural safety concerns. Footpath diversion on designated footpaths in place. Reassessment by end January 2026.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -974,7 +990,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -983,21 +999,21 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.8236</v>
+        <v>51.798</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.5731</v>
+        <v>-1.549</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1007,7 +1023,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal, partial reopening with partial route available, redevelopment ongoing</t>
+          <t>Partial reopening. Path blocked between bridge over River Brent and Brentford Marina on left bank. Redevelopment ongoing, parts now accessible.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1015,13 +1031,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>active partial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1030,10 +1046,57 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.4874</v>
+        <v>51.491</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.3056</v>
+        <v>-0.306</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Benson Weir diversion open</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Diversion in place via Preston Crowmarsh and Howbery Business Park crossing at Wallingford Bridge. Path reopened 1 April 2026.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>reopened</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>51.595</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>-1.132</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge access closure Oxford</t>
+          <t>Osney Bridge diversion Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Access ramp at Botley Road/Osney Bridge closed due to water works. Diversion via Abbey Road in place.</t>
+          <t>Towpath closed ~150 yards before bridge. Diversion via Abbey Road parallel to river, returning via Botley Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -536,26 +536,22 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/diversion-via-abbey-road-due-to-closure-of-access-at-osney-bridge-botley-road-july-2025/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.754</v>
+        <v>51.752</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.254</v>
+        <v>-1.269</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -571,12 +567,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closure Henley</t>
+          <t>Marsh Lock footbridge Henley closure</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety. 3-mile diversion via A4155 between Henley and Shiplake. Order initially until 31 Jan 2026, may be extended.</t>
+          <t>Footbridge closed for safety. Official 2.7-mile diversion via A4155 twice. Order extends beyond 31 Jan 2026, likely to 2027.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -584,17 +580,13 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
+          <t>active-extended</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -606,7 +598,7 @@
         <v>51.526</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.768</v>
+        <v>-0.913</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -627,7 +619,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed by Environment Agency. Diversion via NCN 5.</t>
+          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5 cycle route.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -638,26 +630,22 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
+          <t>https://x.com/ThamesPathNT/status/1915740715797119304</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>51.745</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.308</v>
+        <v>-1.197</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -678,7 +666,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway across weir closed due to corrosion. Rerouted via Abingdon town centre. May reopen at low river levels.</t>
+          <t>Walkway closed at high river flows due to corrosion. Diversion via Abingdon town centre. Reopens during low flows.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -686,25 +674,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>intermittent-high-flow</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/131536/faqs</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.666</v>
+        <v>51.668</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.293</v>
+        <v>-1.289</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -720,12 +708,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure near Marlow</t>
+          <t>Temple Footbridge closure</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed due to structural damage. Diversion via Marlow Bridge and Bisham Abbey.</t>
+          <t>Footbridge closed since May 2023 due to structural decay. Centre span removed Nov 2025. Diversion via Marlow Bridge or Medmenham. Reopening unlikely until 2028.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -733,17 +721,13 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
+          <t>active-extended</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -752,10 +736,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.533</v>
+        <v>51.507</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.788</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -771,12 +755,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 closure near Runnymede M25</t>
+          <t>Bridge 142 Egham closure</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Cast iron bridge closed due to structural cracks. Diversion via A308. Expected closure until 2027.</t>
+          <t>Cast iron bridge damaged by tree strike. Closed Feb 2024. Diversion via A308 and Causeway. May extend to 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -784,35 +768,31 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-01</t>
-        </is>
-      </c>
+          <t>active-extended</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.425</v>
+        <v>51.426</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.523</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -822,12 +802,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir refurbishment works</t>
+          <t>Bell Weir Lock Thames Path diversion</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Small diversion around compound at Runnymede Pleasure Grounds. Bell Weir Lock remains operational. Refurbishment 2026-2027.</t>
+          <t>Small diversion around construction compound at Runnymede Pleasure Grounds for Bell Weir lock refurbishment works. Work planned spring 2026 to autumn 2027.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -838,26 +818,22 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/bell-weir-refurbishment-works-2026-lock-closure-notice/bell-weir-weir-refurbishment-works-2026-lock-closure-notice</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.427</v>
+        <v>51.428</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.508</v>
+        <v>-0.526</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -878,7 +854,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Half-mile towpath closure due to erosion. Diversion via Manor Road and Footpath 227. Unlikely to reopen until late 2026.</t>
+          <t>Half-mile diversion away from Thames due to eroding towpath south of Streatley Bridge. Riverside route unlikely to reopen until late 2026.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -892,19 +868,19 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.613</v>
+        <v>51.616</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.155</v>
+        <v>-1.309</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -925,7 +901,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>No access to island due to diseased trees. Thames Path unaffected.</t>
+          <t>Island closed due to diseased and dangerous trees. Thames Path unaffected but island access denied. Tree clearance planned post-September 2026.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -939,19 +915,19 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.431</v>
+        <v>51.43</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.501</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -967,12 +943,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure Faringdon</t>
+          <t>Ten Foot Bridge Faringdon closure</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed March 2024 due to structural safety concerns. Footpath diversion on designated footpaths in place. Reassessment by end January 2026.</t>
+          <t>Bridge closed March 2024 due to structural and safety concerns. Specialist survey completed. Reopening status pending.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -983,14 +959,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -999,21 +971,21 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.798</v>
+        <v>51.878</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.549</v>
+        <v>-1.512</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1023,7 +995,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Partial reopening. Path blocked between bridge over River Brent and Brentford Marina on left bank. Redevelopment ongoing, parts now accessible.</t>
+          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Area being redeveloped. Partial reopening with workaround route via Thames Lock.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1031,13 +1003,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>partial-open</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1046,57 +1018,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.491</v>
+        <v>51.492</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.306</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Benson Weir diversion open</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Diversion in place via Preston Crowmarsh and Howbery Business Park crossing at Wallingford Bridge. Path reopened 1 April 2026.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>reopened</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>51.595</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>-1.132</v>
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed ~150 yards before bridge. Diversion via Abbey Road parallel to river, returning via Botley Road.</t>
+          <t>Towpath closed about 150 yards before bridge, diversion via Abbey Road and Botley Road</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.752</v>
+        <v>51.7498</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.269</v>
+        <v>-1.2698</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -567,12 +567,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge Henley closure</t>
+          <t>Marsh Lock footbridge closure Henley</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety. Official 2.7-mile diversion via A4155 twice. Order extends beyond 31 Jan 2026, likely to 2027.</t>
+          <t>Bridge closed for safety. Diversion via A4155, approx 3 miles, 1.5 hours. Train/bus available.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -580,13 +580,13 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>active-extended</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.526</v>
+        <v>51.5409</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.913</v>
+        <v>-0.8072</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -609,21 +609,21 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge closure</t>
+          <t>Abingdon Weir closure intermittent</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5 cycle route.</t>
+          <t>Walkway closed due to corrosion, rerouted via Abingdon town centre. May reopen if river level low.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -633,19 +633,19 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://x.com/ThamesPathNT/status/1915740715797119304</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.745</v>
+        <v>51.6729</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.197</v>
+        <v>-1.286</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -656,43 +656,43 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway closure</t>
+          <t>Sandford Footbridge closure near Oxford</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway closed at high river flows due to corrosion. Diversion via Abingdon town centre. Reopens during low flows.</t>
+          <t>Weir damaged in 2022, repairs ongoing. Diversion via Preston Crowmarsh and Wallingford Bridge.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>intermittent-high-flow</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/131536/faqs</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.668</v>
+        <v>51.712</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.289</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -708,12 +708,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure</t>
+          <t>Temple Footbridge closure near Marlow</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed since May 2023 due to structural decay. Centre span removed Nov 2025. Diversion via Marlow Bridge or Medmenham. Reopening unlikely until 2028.</t>
+          <t>Environment Agency deemed bridge unsafe. Closed foreseeable future. Diversion via Bisham Abbey.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -721,31 +721,31 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>active-extended</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.507</v>
+        <v>51.5685</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.788</v>
+        <v>-0.7897</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -755,63 +755,63 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 Egham closure</t>
+          <t>Bell Weir Lock diversion Runnymede</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Cast iron bridge damaged by tree strike. Closed Feb 2024. Diversion via A308 and Causeway. May extend to 2027.</t>
+          <t>Thames Path diverted at Runnymede. Diversion via A308 pavements.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>136.5</v>
+        <v>136.2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>active-extended</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.426</v>
+        <v>51.4292</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.523</v>
+        <v>-0.5543</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock Thames Path diversion</t>
+          <t>Runnymede Bridge 142 closure Egham</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Small diversion around construction compound at Runnymede Pleasure Grounds for Bell Weir lock refurbishment works. Work planned spring 2026 to autumn 2027.</t>
+          <t>Diversion uses A308 pavements, 0.6 miles added distance. May extend until 2027.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>136.2</v>
+        <v>136.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -821,91 +821,91 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.428</v>
+        <v>51.4285</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.526</v>
+        <v>-0.553</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath diversion</t>
+          <t>Penton Hook Island closure Runnymede</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Half-mile diversion away from Thames due to eroding towpath south of Streatley Bridge. Riverside route unlikely to reopen until late 2026.</t>
+          <t>No access to island due to diseased trees. Thames Path unaffected.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>81.5</v>
+        <v>135.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.616</v>
+        <v>51.4343</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.309</v>
+        <v>-0.5648</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure</t>
+          <t>Streatley-Goring towpath diversion</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island closed due to diseased and dangerous trees. Thames Path unaffected but island access denied. Tree clearance planned post-September 2026.</t>
+          <t>Towpath closed due to narrow/flood-prone section. Diversion via Manor Road.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>135.6</v>
+        <v>81.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -915,40 +915,36 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.43</v>
+        <v>51.5208</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.52</v>
+        <v>-1.3108</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge Faringdon closure</t>
+          <t>Ten Foot Bridge closure Faringdon</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed March 2024 due to structural and safety concerns. Specialist survey completed. Reopening status pending.</t>
+          <t>Status unconfirmed - no recent information found. Further investigation needed.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -956,25 +952,21 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>unconfirmed</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n">
-        <v>51.878</v>
+        <v>51.3089</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.512</v>
+        <v>-1.567</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -995,7 +987,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Area being redeveloped. Partial reopening with workaround route via Thames Lock.</t>
+          <t>Path blocked on left bank between Brent bridge and Brentford Marina. Parts now open via alternatives.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1003,13 +995,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>partial-open</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1018,10 +1010,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.492</v>
+        <v>51.4905</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.307</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -510,14 +510,14 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Osney Bridge diversion Oxford</t>
@@ -525,7 +525,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed about 150 yards before bridge, diversion via Abbey Road and Botley Road</t>
+          <t>Towpath closed about 150 yards from bridge. Diversion via Abbey Road parallel to river. Reopen via Botley Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.7498</v>
+        <v>51.749</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.2698</v>
+        <v>-1.273</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -572,7 +572,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed for safety. Diversion via A4155, approx 3 miles, 1.5 hours. Train/bus available.</t>
+          <t>Footbridge closed for safety. 3-mile diversion via A4155 required. 1hr 30min walk. Trains available between Henley-Shiplake. Order until 31 Jan 2026.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -583,10 +583,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,10 +599,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.5409</v>
+        <v>51.481</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.8072</v>
+        <v>-0.925</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -609,21 +613,21 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir closure intermittent</t>
+          <t>Sandford Footbridge closure</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Walkway closed due to corrosion, rerouted via Abingdon town centre. May reopen if river level low.</t>
+          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5 route. April 2025 announcement.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -633,19 +637,19 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://x.com/ThamesPathNT/status/1915740715797119304</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.6729</v>
+        <v>51.649</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.286</v>
+        <v>-1.182</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -656,21 +660,21 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge closure near Oxford</t>
+          <t>Abingdon Weir walkway closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weir damaged in 2022, repairs ongoing. Diversion via Preston Crowmarsh and Wallingford Bridge.</t>
+          <t>Walkway across weir closed due to corrosion. Path re-routed via Abingdon town centre. May reopen if river level is low but closes when river levels rise.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -680,7 +684,7 @@
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -689,10 +693,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.712</v>
+        <v>51.607</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.31</v>
+        <v>-1.292</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -713,7 +717,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Environment Agency deemed bridge unsafe. Closed foreseeable future. Diversion via Bisham Abbey.</t>
+          <t>Closed May 2023 due to structural damage. Unlikely to reopen until 2028. Diversion via Marlow Bridge and Bisham. Central span removed Nov 2025, both side spans in poor condition.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -727,44 +731,44 @@
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.thamespath.org.uk/2025/12/04/temple-bridge-closed-until-2028-at-least/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.5685</v>
+        <v>51.453</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.7897</v>
+        <v>-0.851</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion Runnymede</t>
+          <t>Bridge 142 closure Runnymede Egham</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Thames Path diverted at Runnymede. Diversion via A308 pavements.</t>
+          <t>Closed Feb 2024 after tree strike. Structural fault. Diversion via Causeway and Runnymede Roundabout. Expected until 2027. Minimal 0.6 miles added.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>136.2</v>
+        <v>136.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -774,44 +778,44 @@
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.4292</v>
+        <v>51.406</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5543</v>
+        <v>-0.573</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Runnymede Bridge 142 closure Egham</t>
+          <t>Bell Weir Lock refurbishment diversion</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Diversion uses A308 pavements, 0.6 miles added distance. May extend until 2027.</t>
+          <t>Small diversion around compound with construction machinery for Bell Weir lock works. Keep compound on left, soon back to river. Works spring 2026-autumn 2027.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>136.5</v>
+        <v>136.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -821,7 +825,7 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -830,31 +834,31 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.4285</v>
+        <v>51.408</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.553</v>
+        <v>-0.574</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>closure</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>closure</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure Runnymede</t>
+          <t>Penton Hook Island access closed</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>No access to island due to diseased trees. Thames Path unaffected.</t>
+          <t>No access to island due to diseased trees. Thames Path itself unaffected. Access point closed but main path continues.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -862,13 +866,13 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -877,23 +881,23 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.4343</v>
+        <v>51.412</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.5648</v>
+        <v>-0.555</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Streatley-Goring towpath diversion</t>
@@ -901,7 +905,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed due to narrow/flood-prone section. Diversion via Manor Road.</t>
+          <t>Half-mile (0.8km) diversion from eroding riverside towpath. Funding insufficient, repairs unlikely until late 2026. Path narrow and frequently floods.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -915,93 +919,105 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.5208</v>
+        <v>51.52</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-1.3108</v>
+        <v>-1.305</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n"/>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>diversion</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure Faringdon</t>
+          <t>Brentford Grand Union Canal disruption</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Status unconfirmed - no recent information found. Further investigation needed.</t>
+          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Area being redeveloped. Parts now open via alternate route via Thames Lock. No official diversion.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34</v>
+        <v>154</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>unconfirmed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="n">
-        <v>51.3089</v>
+        <v>51.481</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.567</v>
+        <v>-0.319</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal disruption</t>
+          <t>Wallingford Weir path reopened</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank between Brent bridge and Brentford Marina. Parts now open via alternatives.</t>
+          <t>Thames Path reopened on 1 April 2026. Previously had diversion via Preston Crowmarsh and Howbery Business Park crossing at Wallingford Bridge.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n"/>
+          <t>reopened</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1010,10 +1026,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.4905</v>
+        <v>51.597</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.307</v>
+        <v>-1.128</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge diversion Oxford</t>
+          <t>Osney Bridge towpath diversion Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed about 150 yards from bridge. Diversion via Abbey Road parallel to river. Reopen via Botley Road.</t>
+          <t>Towpath closed ~150 yards before bridge. Diversion via Abbey Road to Botley Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.749</v>
+        <v>51.752</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>-1.273</v>
@@ -567,12 +567,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closure Henley</t>
+          <t>Marsh Lock Horsebridge closure Henley</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety. 3-mile diversion via A4155 required. 1hr 30min walk. Trains available between Henley-Shiplake. Order until 31 Jan 2026.</t>
+          <t>Footbridge closed due to safety concerns. 3-mile diversion via A4155 pavement.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -583,14 +583,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -599,10 +595,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.481</v>
+        <v>51.475</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.925</v>
+        <v>-0.903</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -623,7 +619,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5 route. April 2025 announcement.</t>
+          <t>Unsafe footbridge closed north of Sandford Lock. Diversion via NCN 5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -637,7 +633,7 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -646,10 +642,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.649</v>
+        <v>51.655</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.182</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -665,12 +661,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway closure</t>
+          <t>Abingdon Weir walkway intermittent closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway across weir closed due to corrosion. Path re-routed via Abingdon town centre. May reopen if river level is low but closes when river levels rise.</t>
+          <t>Walkway closed when river levels high. Due to corrosion. Re-routed via town centre.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -684,7 +680,7 @@
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -693,10 +689,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.607</v>
+        <v>51.667</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.292</v>
+        <v>-1.283</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -707,7 +703,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -717,7 +713,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Closed May 2023 due to structural damage. Unlikely to reopen until 2028. Diversion via Marlow Bridge and Bisham. Central span removed Nov 2025, both side spans in poor condition.</t>
+          <t>Bridge closed since May 2023 due to structural concerns. Unlikely reopened until 2028.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -728,10 +724,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.453</v>
+        <v>51.552</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.851</v>
+        <v>-0.797</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -759,12 +759,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 closure Runnymede Egham</t>
+          <t>Bridge 142 closure Egham</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Closed Feb 2024 after tree strike. Structural fault. Diversion via Causeway and Runnymede Roundabout. Expected until 2027. Minimal 0.6 miles added.</t>
+          <t>Footbridge closure due to tree damage. Diversion via A308/Causeway.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -775,10 +775,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -787,16 +791,16 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.406</v>
+        <v>51.425</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.573</v>
+        <v>-0.525</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -806,12 +810,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock refurbishment diversion</t>
+          <t>Bell Weir Lock diversion Runnymede</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Small diversion around compound with construction machinery for Bell Weir lock works. Keep compound on left, soon back to river. Works spring 2026-autumn 2027.</t>
+          <t>Thames Path diverted around construction compound at Runnymede Pleasure Grounds.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -825,7 +829,7 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -834,35 +838,35 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.408</v>
+        <v>51.426</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.574</v>
+        <v>-0.533</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island access closed</t>
+          <t>Streatley-Goring towpath diversion</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>No access to island due to diseased trees. Thames Path itself unaffected. Access point closed but main path continues.</t>
+          <t>Eroded towpath diverted inland. Unlikely to reopen until late 2026.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135.6</v>
+        <v>81.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -872,19 +876,19 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.412</v>
+        <v>51.522</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.555</v>
+        <v>-1.143</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -895,21 +899,21 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath diversion</t>
+          <t>Penton Hook Island closure</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Half-mile (0.8km) diversion from eroding riverside towpath. Funding insufficient, repairs unlikely until late 2026. Path narrow and frequently floods.</t>
+          <t>Island closed due to diseased trees. Thames Path unaffected but island inaccessible.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>81.5</v>
+        <v>135.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -919,19 +923,19 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.52</v>
+        <v>51.431</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-1.305</v>
+        <v>-0.457</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -942,82 +946,82 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal disruption</t>
+          <t>Ten Foot Bridge closure Faringdon</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Area being redeveloped. Parts now open via alternate route via Thames Lock. No official diversion.</t>
+          <t>Bridge closed March 2024 due to structural safety concerns. No reopening date.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>154</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.481</v>
+        <v>51.694</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-0.319</v>
+        <v>-1.489</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Wallingford Weir path reopened</t>
+          <t>Brentford Grand Union Canal disruption</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Thames Path reopened on 1 April 2026. Previously had diversion via Preston Crowmarsh and Howbery Business Park crossing at Wallingford Bridge.</t>
+          <t>Path blocked on left bank of Grand Union Canal between Brent and Brentford Marina.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>reopened</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1026,10 +1030,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.597</v>
+        <v>51.49</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-1.128</v>
+        <v>-0.295</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -510,7 +510,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge towpath diversion Oxford</t>
+          <t>Osney Bridge diversion</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed ~150 yards before bridge. Diversion via Abbey Road to Botley Road.</t>
+          <t>Towpath closed about 150 yards before bridge. Diversion via Abbey Road parallel to river, reconnecting at Botley Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.752</v>
+        <v>51.7543</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.273</v>
+        <v>-1.2783</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -567,12 +567,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock Horsebridge closure Henley</t>
+          <t>Marsh Lock footbridge closure</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed due to safety concerns. 3-mile diversion via A4155 pavement.</t>
+          <t>Footbridge closed on safety grounds. 3-mile diversion via A4155 with red pedestrian signs. Train/bus available.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -583,10 +583,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,10 +599,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.475</v>
+        <v>51.5255</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.903</v>
+        <v>-0.9133</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -619,7 +623,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge closed north of Sandford Lock. Diversion via NCN 5.</t>
+          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -633,7 +637,7 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -642,10 +646,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.655</v>
+        <v>51.7286</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.24</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -666,7 +670,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway closed when river levels high. Due to corrosion. Re-routed via town centre.</t>
+          <t>Walkway closed due to corrosion. Reopens if river levels low, closes when levels rise. Re-routed via Abingdon town centre.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -674,13 +678,13 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -689,10 +693,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.667</v>
+        <v>51.6693</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.283</v>
+        <v>-1.3027</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -708,12 +712,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure near Marlow</t>
+          <t>Temple Footbridge closure</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed since May 2023 due to structural concerns. Unlikely reopened until 2028.</t>
+          <t>Closed May 2023 for structural repairs. Central span removed Nov 2025. Unlikely to reopen until 2028. Diversion via Marlow Bridge.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -731,19 +735,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/04/temple-bridge-closed-until-2028-at-least/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.552</v>
+        <v>51.5132</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.797</v>
+        <v>-0.8272</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -759,12 +763,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 closure Egham</t>
+          <t>Bridge 142 (Runnymede Bridge 142) closure</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closure due to tree damage. Diversion via A308/Causeway.</t>
+          <t>Bridge closed Feb 2024 due to structural damage. Diversion via A308 and Egham roundabout. Expected closure until 2026 minimum.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -782,7 +786,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -791,16 +795,16 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.425</v>
+        <v>51.4249</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.525</v>
+        <v>-0.5293</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -810,12 +814,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion Runnymede</t>
+          <t>Bell Weir Lock diversion</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thames Path diverted around construction compound at Runnymede Pleasure Grounds.</t>
+          <t>Small diversion around compound with machinery used for Bell Weir lock refurbishment works near Queen Elizabeth statue at Runnymede.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -829,7 +833,7 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -838,16 +842,16 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.426</v>
+        <v>51.4268</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.533</v>
+        <v>-0.5368000000000001</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -862,7 +866,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Eroded towpath diverted inland. Unlikely to reopen until late 2026.</t>
+          <t>Path closed about 1/4 mile downstream of Goring. Small diversion onto parallel Manor Road with footpath returning to river.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -876,40 +880,40 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.522</v>
+        <v>51.6119</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.143</v>
+        <v>-1.4889</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure</t>
+          <t>Penton Hook Island access closure</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island closed due to diseased trees. Thames Path unaffected but island inaccessible.</t>
+          <t>No access to island due to diseased trees. Thames Path on main bank unaffected.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -923,19 +927,19 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.431</v>
+        <v>51.4319</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.457</v>
+        <v>-0.4878</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -951,12 +955,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure Faringdon</t>
+          <t>Ten Foot Bridge closure</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed March 2024 due to structural safety concerns. No reopening date.</t>
+          <t>Bridge closed March 2024 due to structural and safety concerns. Located between Rushey and Shifford locks near Buckland, Faringdon.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -974,7 +978,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -983,16 +987,16 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.694</v>
+        <v>51.8451</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.489</v>
+        <v>-1.5724</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1007,7 +1011,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between Brent and Brentford Marina.</t>
+          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Parts now open via alternate routing through The Ham.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1021,7 +1025,7 @@
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1030,10 +1034,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.49</v>
+        <v>51.4879</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.295</v>
+        <v>-0.3018</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge diversion</t>
+          <t>Osney Bridge diversion Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed about 150 yards before bridge. Diversion via Abbey Road parallel to river, reconnecting at Botley Road.</t>
+          <t>Towpath closed approximately 150 yards before Osney Bridge. Diversion via Abbey Road parallel to river, rejoin at Botley Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.7543</v>
+        <v>51.7519</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.2783</v>
+        <v>-1.2667</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -562,17 +562,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closure</t>
+          <t>Marsh Lock footbridge closure Henley</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed on safety grounds. 3-mile diversion via A4155 with red pedestrian signs. Train/bus available.</t>
+          <t>Footbridge closed on safety grounds by Environment Agency. 3-mile diversion via A4155 pavements. Train/bus alternative between Henley-Shiplake.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -583,14 +583,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -599,16 +595,16 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.5255</v>
+        <v>51.5348</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.9133</v>
+        <v>-0.8089</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -618,12 +614,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge closure</t>
+          <t>Sandford Footbridge closure mile 57</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5.</t>
+          <t>Weir damaged in 2022 and currently being repaired. Diversion via Preston Crowmarsh, Howbery Business Park, crossing at Wallingford Bridge.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -637,19 +633,19 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://x.com/ThamesPathNT/status/1915740715797119304</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.7286</v>
+        <v>51.6137</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.1851</v>
+        <v>-1.1375</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -665,12 +661,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway intermittent closure</t>
+          <t>Abingdon Weir intermittent closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway closed due to corrosion. Reopens if river levels low, closes when levels rise. Re-routed via Abingdon town centre.</t>
+          <t>Walkway across weir closed due to corrosion. Rerouted via Abingdon town centre. May reopen at low river levels but closes again when levels rise.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -678,13 +674,13 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -693,10 +689,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.6693</v>
+        <v>51.5724</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.3027</v>
+        <v>-1.2908</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -707,17 +703,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure</t>
+          <t>Temple Footbridge closure near Marlow</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Closed May 2023 for structural repairs. Central span removed Nov 2025. Unlikely to reopen until 2028. Diversion via Marlow Bridge.</t>
+          <t>Bridge deemed unsafe and closed foreseeable future. Diversion via Marlow Bridge or Hambledon Lock through Medmenham/Harleyford. Extended until 2027.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -728,14 +724,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -744,16 +736,16 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.5132</v>
+        <v>51.5741</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.8272</v>
+        <v>-0.8042</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -763,12 +755,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 (Runnymede Bridge 142) closure</t>
+          <t>Runnymede Bridge 142 closure Egham</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed Feb 2024 due to structural damage. Diversion via A308 and Egham roundabout. Expected closure until 2026 minimum.</t>
+          <t>A308 pavement diversion via Egham roundabout and underpass, returning to riverbank before Staines. Expected duration until 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -779,47 +771,43 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-01</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.4249</v>
+        <v>51.4328</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5293</v>
+        <v>-0.5497</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion</t>
+          <t>Bell Weir Lock diversion Runnymede</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Small diversion around compound with machinery used for Bell Weir lock refurbishment works near Queen Elizabeth statue at Runnymede.</t>
+          <t>Refurbishment works. Restriction notice issued. Navigation restrictions in place around Bell Weir.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -833,30 +821,30 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.gov.uk/guidance/river-thames-restrictions-and-closures</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.4268</v>
+        <v>51.435</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.5558</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -866,7 +854,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Path closed about 1/4 mile downstream of Goring. Small diversion onto parallel Manor Road with footpath returning to river.</t>
+          <t>Path narrow and frequently floods. Diversion via Footpath 227 east to Manor Road. Riverside route unlikely to reopen until late 2026.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -880,40 +868,40 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.6119</v>
+        <v>51.5183</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.4889</v>
+        <v>-1.3017</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island access closure</t>
+          <t>Penton Hook Island closure</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>No access to island due to diseased trees. Thames Path on main bank unaffected.</t>
+          <t>No access to island due to diseased trees. Thames Path unaffected by island closure.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -927,7 +915,7 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -936,10 +924,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.4319</v>
+        <v>51.4431</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.4878</v>
+        <v>-0.5264</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -955,12 +943,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure</t>
+          <t>Ten Foot Bridge closure Faringdon</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed March 2024 due to structural and safety concerns. Located between Rushey and Shifford locks near Buckland, Faringdon.</t>
+          <t>Bridge closure noted in route descriptions. Status current as of June 2026.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -968,42 +956,38 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/trails/thames-path/route/</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.8451</v>
+        <v>51.6592</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.5724</v>
+        <v>-1.5639</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Brentford Grand Union Canal disruption</t>
@@ -1011,7 +995,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Parts now open via alternate routing through The Ham.</t>
+          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Area being redeveloped. Parts now open via The Ham, Thames Lock route.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1025,7 +1009,7 @@
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1034,10 +1018,57 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.4879</v>
+        <v>51.4887</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.3018</v>
+        <v>-0.3092</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Benson Weir walkway closure diversion</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Walkway across Benson Weir closed to public due to safety concerns. Diversion route in place via Preston Crowmarsh.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nationaltrail.co.uk/en_GB/trails/thames-path/news/</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>51.5456</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>-1.1158</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge diversion Oxford</t>
+          <t>Osney Bridge Oxford towpath closure</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed approximately 150 yards before Osney Bridge. Diversion via Abbey Road parallel to river, rejoin at Botley Road.</t>
+          <t>Thames Path towpath closed about 150 yards from bridge. Diversion via Abbey Road parallel to river, then Botley Road back to bridge.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.7519</v>
+        <v>51.753</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.2667</v>
+        <v>-1.271</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -567,12 +567,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closure Henley</t>
+          <t>Marsh Lock footbridge Henley closure</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed on safety grounds by Environment Agency. 3-mile diversion via A4155 pavements. Train/bus alternative between Henley-Shiplake.</t>
+          <t>Footbridge closed for safety. Environment Agency 2.7 mile diversion via A4155. Initially until 31 Jan 2026, may be extended.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -583,10 +583,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,31 +599,31 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.5348</v>
+        <v>51.506</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.8089</v>
+        <v>-0.831</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge closure mile 57</t>
+          <t>Sandford Footbridge closure</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Weir damaged in 2022 and currently being repaired. Diversion via Preston Crowmarsh, Howbery Business Park, crossing at Wallingford Bridge.</t>
+          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -630,22 +634,26 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.6137</v>
+        <v>51.619</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.1375</v>
+        <v>-1.132</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -661,12 +669,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir intermittent closure</t>
+          <t>Abingdon Weir walkway intermittent closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway across weir closed due to corrosion. Rerouted via Abingdon town centre. May reopen at low river levels but closes again when levels rise.</t>
+          <t>Weir walkway closed due to corrosion, diverted via Abingdon town centre. Opens when river levels low, closes at high flow.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -674,13 +682,13 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -689,10 +697,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.5724</v>
+        <v>51.46</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.2908</v>
+        <v>-1.292</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -703,17 +711,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure near Marlow</t>
+          <t>Temple Footbridge Marlow closure</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bridge deemed unsafe and closed foreseeable future. Diversion via Marlow Bridge or Hambledon Lock through Medmenham/Harleyford. Extended until 2027.</t>
+          <t>Bridge closed May 2023 for structural safety. Diversion via Marlow Bridge &amp; Bisham or Hambleden Lock route.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -724,10 +732,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -736,21 +748,21 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.5741</v>
+        <v>51.417</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.8042</v>
+        <v>-0.742</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -760,7 +772,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>A308 pavement diversion via Egham roundabout and underpass, returning to riverbank before Staines. Expected duration until 2027.</t>
+          <t>Footbridge south of Runnymede Bridge closed due to structural damage. Diversion via A308 towards A30 and M25.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -771,28 +783,32 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.4328</v>
+        <v>51.417</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5497</v>
+        <v>-0.549</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -802,12 +818,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion Runnymede</t>
+          <t>Bell Weir Lock Thames Path diversion</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Refurbishment works. Restriction notice issued. Navigation restrictions in place around Bell Weir.</t>
+          <t>Small diversion around construction compound at Runnymede Pleasure Grounds during Bell Weir refurbishment. Works spring 2026-autumn 2027.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -818,33 +834,37 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/guidance/river-thames-restrictions-and-closures</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.435</v>
+        <v>51.409</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.5558</v>
+        <v>-0.556</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -854,7 +874,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Path narrow and frequently floods. Diversion via Footpath 227 east to Manor Road. Riverside route unlikely to reopen until late 2026.</t>
+          <t>Section closed for repairs. Diversion inland on footpath from blocked towpath to Manor Road, then back via footpath to river.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -868,7 +888,7 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -877,23 +897,19 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.5183</v>
+        <v>51.327</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.3017</v>
+        <v>-1.242</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>closure</t>
-        </is>
-      </c>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Penton Hook Island closure</t>
@@ -901,7 +917,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>No access to island due to diseased trees. Thames Path unaffected by island closure.</t>
+          <t>No access to island due to diseased trees. Thames Path unaffected.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -915,7 +931,7 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -924,10 +940,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.4431</v>
+        <v>51.413</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.5264</v>
+        <v>-0.534</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -943,12 +959,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure Faringdon</t>
+          <t>Ten Foot Bridge Faringdon closure</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bridge closure noted in route descriptions. Status current as of June 2026.</t>
+          <t>Bridge between Rushey and Shifford locks near Buckland closed March 2024 due to structural safety concerns.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -956,31 +972,35 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/trails/thames-path/route/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.6592</v>
+        <v>51.666</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.5639</v>
+        <v>-1.542</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -995,7 +1015,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Area being redeveloped. Parts now open via The Ham, Thames Lock route.</t>
+          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Redevelopment ongoing. Partial reopening with alternative route via The Ham.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1009,7 +1029,7 @@
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1018,16 +1038,16 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.4887</v>
+        <v>51.485</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.3092</v>
+        <v>-0.306</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,38 +1057,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Benson Weir walkway closure diversion</t>
+          <t>Benson Weir footbridge reopened</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Walkway across Benson Weir closed to public due to safety concerns. Diversion route in place via Preston Crowmarsh.</t>
+          <t>Benson Weir footbridge reopened April 1 2026 after 3+ year closure. Completely replaced. Thames Path now open.</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>76.5</v>
+        <v>75</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/trails/thames-path/news/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>51.5456</v>
+        <v>51.427</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>-1.1158</v>
+        <v>-1.104</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge Oxford towpath closure</t>
+          <t>Osney Bridge towpath diversion Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Thames Path towpath closed about 150 yards from bridge. Diversion via Abbey Road parallel to river, then Botley Road back to bridge.</t>
+          <t>Towpath closed about 150 yards from bridge. Diversion via Abbey Road returns to Osney Bridge via Botley Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -536,10 +536,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +552,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.753</v>
+        <v>51.7497</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.271</v>
+        <v>-1.2581</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -567,12 +571,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge Henley closure</t>
+          <t>Marsh Lock footbridge closure Henley</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety. Environment Agency 2.7 mile diversion via A4155. Initially until 31 Jan 2026, may be extended.</t>
+          <t>Environment Agency closed footbridge on safety grounds. 3-mile diversion via A4155 pavements between Henley and Shiplake. Diversion may extend until 2026-31-01.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -585,12 +589,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -599,10 +603,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.506</v>
+        <v>51.5326</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.831</v>
+        <v>-0.8976</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -623,7 +627,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5.</t>
+          <t>Unsafe footbridge closed north (upstream) of Sandford Lock. Diversion via NCN 5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -636,12 +640,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -650,10 +654,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.619</v>
+        <v>51.8148</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.132</v>
+        <v>-1.1465</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -669,12 +673,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway intermittent closure</t>
+          <t>Abingdon Weir walkway closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weir walkway closed due to corrosion, diverted via Abingdon town centre. Opens when river levels low, closes at high flow.</t>
+          <t>Walkway closed due to corrosion. Path re-routed via Abingdon town centre. May reopen if river levels drop but will close again when levels rise.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -682,13 +686,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -697,10 +705,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.46</v>
+        <v>51.7728</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.292</v>
+        <v>-1.2882</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -716,12 +724,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge Marlow closure</t>
+          <t>Temple Footbridge closure near Marlow</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed May 2023 for structural safety. Diversion via Marlow Bridge &amp; Bisham or Hambleden Lock route.</t>
+          <t>Environment Agency deemed bridge unsafe. Closed for foreseeable future. Follow diversion to Bisham Abbey then minor roads to Marlow.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -734,24 +742,24 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.417</v>
+        <v>51.5819</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.742</v>
+        <v>-0.7987</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -767,12 +775,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Runnymede Bridge 142 closure Egham</t>
+          <t>Bridge 142 (Runnymede) closure Egham</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Footbridge south of Runnymede Bridge closed due to structural damage. Diversion via A308 towards A30 and M25.</t>
+          <t>Cast iron bridge hit by tree in 2023, closed Feb 2024 with cracks detected. Diversion via River Park Ave &amp; pavements on A308/Causeway. Expected until 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -785,12 +793,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -799,31 +807,31 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.417</v>
+        <v>51.4336</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.549</v>
+        <v>-0.5373</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock Thames Path diversion</t>
+          <t>Bell Weir Lock diversion Runnymede</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Small diversion around construction compound at Runnymede Pleasure Grounds during Bell Weir refurbishment. Works spring 2026-autumn 2027.</t>
+          <t>Thames Path temporarily diverted at Runnymede Pleasure Ground during weir refurbishment. Work 2026 spring to autumn 2027. Lock remains operational.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -836,12 +844,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -850,125 +858,137 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.409</v>
+        <v>51.4346</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.556</v>
+        <v>-0.5387999999999999</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>null</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath diversion</t>
+          <t>Penton Hook Island Thames Path unaffected</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Section closed for repairs. Diversion inland on footpath from blocked towpath to Manor Road, then back via footpath to river.</t>
+          <t>No access to island due to diseased trees. Thames Path unaffected by closure.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>81.5</v>
+        <v>135.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n"/>
+          <t>reopened</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.327</v>
+        <v>51.4397</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.242</v>
+        <v>-0.5266999999999999</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>closure</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure</t>
+          <t>Ten Foot Bridge closure Faringdon</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>No access to island due to diseased trees. Thames Path unaffected.</t>
+          <t>Ten Foot bridge crosses Thames between Rushey and Shifford locks near Buckland/Faringdon. Closed March 2024 due to structural safety concerns. Specialist survey completed.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>135.6</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.413</v>
+        <v>51.9148</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.534</v>
+        <v>-1.5721</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge Faringdon closure</t>
+          <t>Brentford Grand Union Canal disruption</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bridge between Rushey and Shifford locks near Buckland closed March 2024 due to structural safety concerns.</t>
+          <t>Path blocked on left bank of Grand Union Canal (between River Brent bridge and Brentford Marina). Partial reopening: walk Ham, cross canal, follow to Thames Lock, cross back, follow Dock Road.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34</v>
+        <v>154</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -977,24 +997,24 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.666</v>
+        <v>51.4898</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.542</v>
+        <v>-0.3076</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -1010,38 +1030,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal disruption</t>
+          <t>Streatley-Goring towpath diversion</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Redevelopment ongoing. Partial reopening with alternative route via The Ham.</t>
+          <t>Half mile diversion from towpath due to eroding towpath. Follows inland Manor Road footpath. Riverside route unlikely to reopen until late 2026.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>154</v>
+        <v>81.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.485</v>
+        <v>51.6294</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.306</v>
+        <v>-1.099</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -1052,25 +1076,25 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Benson Weir footbridge reopened</t>
+          <t>Benson Weir walkway reopened</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Benson Weir footbridge reopened April 1 2026 after 3+ year closure. Completely replaced. Thames Path now open.</t>
+          <t>Footbridge over Benson Weir reopened 2026-04-01 after 3+ year closure for safety. Completely replaced with upgraded weir including fish pass.</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>75</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>reopened</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1080,19 +1104,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.yahoo.com/news/articles/thames-footbridge-reopens-three-closure-052431857.html</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>51.427</v>
+        <v>51.6702</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>-1.104</v>
+        <v>-1.0854</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -510,22 +510,22 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge towpath diversion Oxford</t>
+          <t>Osney Bridge diversion</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed about 150 yards from bridge. Diversion via Abbey Road returns to Osney Bridge via Botley Road.</t>
+          <t>Towpath closed about 150 yards upstream, diversion via Abbey Road and Botley Road</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -536,14 +536,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -552,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.7497</v>
+        <v>51.7487</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.2581</v>
+        <v>-1.2676</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -566,17 +562,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closure Henley</t>
+          <t>Marsh Lock footbridge closure</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Environment Agency closed footbridge on safety grounds. 3-mile diversion via A4155 pavements between Henley and Shiplake. Diversion may extend until 2026-31-01.</t>
+          <t>Footbridge closed for safety, diversion via A4155 pavements, ~3 miles, may extend beyond Jan 2026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -587,14 +583,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -603,10 +595,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.5326</v>
+        <v>51.5333</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.8976</v>
+        <v>-0.8958</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -617,7 +609,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -627,7 +619,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge closed north (upstream) of Sandford Lock. Diversion via NCN 5.</t>
+          <t>Unsafe footbridge closed upstream of Sandford Lock, diversion via NCN 5</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -638,14 +630,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -654,10 +642,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.8148</v>
+        <v>51.7292</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.1465</v>
+        <v>-1.0906</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -678,7 +666,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway closed due to corrosion. Path re-routed via Abingdon town centre. May reopen if river levels drop but will close again when levels rise.</t>
+          <t>Walkway across weir closed due to corrosion, rerouted via town centre, reopens at low water levels</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -689,14 +677,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -705,10 +689,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.7728</v>
+        <v>51.6748</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.2882</v>
+        <v>-1.2887</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -719,17 +703,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure near Marlow</t>
+          <t>Temple Footbridge closure</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Environment Agency deemed bridge unsafe. Closed for foreseeable future. Follow diversion to Bisham Abbey then minor roads to Marlow.</t>
+          <t>Environment Agency closed for safety. Divert via Bisham Abbey and minor roads to Marlow</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -740,14 +724,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -756,10 +736,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.5819</v>
+        <v>51.5222</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.7987</v>
+        <v>-0.8171</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -770,17 +750,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 (Runnymede) closure Egham</t>
+          <t>Runnymede Bridge 142 closure</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Cast iron bridge hit by tree in 2023, closed Feb 2024 with cracks detected. Diversion via River Park Ave &amp; pavements on A308/Causeway. Expected until 2027.</t>
+          <t>Footbridge closed, diversion via A308 pavements, extended to 2027</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -791,14 +771,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -807,10 +783,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.4336</v>
+        <v>51.4298</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5373</v>
+        <v>-0.5431</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -826,12 +802,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion Runnymede</t>
+          <t>Bell Weir Lock refurbishment</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thames Path temporarily diverted at Runnymede Pleasure Ground during weir refurbishment. Work 2026 spring to autumn 2027. Lock remains operational.</t>
+          <t>Thames Path diverted at Runnymede Pleasure Ground during refurbishment works April 2026-Autumn 2027</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -844,12 +820,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -858,35 +834,35 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.4346</v>
+        <v>51.4285</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.546</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island Thames Path unaffected</t>
+          <t>Streatley-Goring towpath diversion</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>No access to island due to diseased trees. Thames Path unaffected by closure.</t>
+          <t>Path reopened after resurfacing March 2026, previously diverted</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135.6</v>
+        <v>81.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -895,24 +871,24 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.4397</v>
+        <v>51.6121</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-1.3076</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -923,72 +899,68 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure Faringdon</t>
+          <t>Penton Hook Island closure</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot bridge crosses Thames between Rushey and Shifford locks near Buckland/Faringdon. Closed March 2024 due to structural safety concerns. Specialist survey completed.</t>
+          <t>No access to island due to diseased trees, Thames Path unaffected</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34</v>
+        <v>135.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.9148</v>
+        <v>51.4293</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-1.5721</v>
+        <v>-0.5207000000000001</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal disruption</t>
+          <t>Ten Foot Bridge closure</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal (between River Brent bridge and Brentford Marina). Partial reopening: walk Ham, cross canal, follow to Thames Lock, cross back, follow Dock Road.</t>
+          <t>Structurally unsafe, closed March 2024, full specialist survey completed pending resolution</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>154</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -997,75 +969,71 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.4898</v>
+        <v>51.7912</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-0.3076</v>
+        <v>-1.5715</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath diversion</t>
+          <t>Brentford Grand Union Canal disruption</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Half mile diversion from towpath due to eroding towpath. Follows inland Manor Road footpath. Riverside route unlikely to reopen until late 2026.</t>
+          <t>Left bank path blocked during redevelopment, parts now open via alternative routes through canal</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>81.5</v>
+        <v>154</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.6294</v>
+        <v>51.4891</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-1.099</v>
+        <v>-0.3081</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -1076,7 +1044,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1086,11 +1054,11 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Footbridge over Benson Weir reopened 2026-04-01 after 3+ year closure for safety. Completely replaced with upgraded weir including fish pass.</t>
+          <t>Footbridge reopened April 1, 2026 after 3+ years closed for repairs, diversion removed</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1104,19 +1072,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.yahoo.com/news/articles/thames-footbridge-reopens-three-closure-052431857.html</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>51.6702</v>
+        <v>51.6161</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>-1.0854</v>
+        <v>-1.1389</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge diversion</t>
+          <t>Osney Bridge Diversion</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed about 150 yards upstream, diversion via Abbey Road and Botley Road</t>
+          <t>Towpath closed 150 yards before bridge. Diversion via Abbey Road parallel to river.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -533,13 +533,13 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.7487</v>
+        <v>51.752694</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.2676</v>
+        <v>-1.273093</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -567,12 +567,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closure</t>
+          <t>Marsh Lock Footbridge Closure</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety, diversion via A4155 pavements, ~3 miles, may extend beyond Jan 2026</t>
+          <t>Footbridge closed for safety. 3-mile diversion via A4155 pavements. Train/bus available.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -580,13 +580,13 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Active - extends beyond Jan 2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.5333</v>
+        <v>51.457</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.8958</v>
+        <v>-0.903</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -614,12 +614,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge closure</t>
+          <t>Sandford Footbridge Closure</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge closed upstream of Sandford Lock, diversion via NCN 5</t>
+          <t>Unsafe footbridge closed. Diversion via NCN Route 5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -627,13 +627,13 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.7292</v>
+        <v>51.662</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.0906</v>
+        <v>-1.179</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -661,12 +661,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway closure</t>
+          <t>Abingdon Weir Walkway</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway across weir closed due to corrosion, rerouted via town centre, reopens at low water levels</t>
+          <t>Closed when river levels high/fast. Reopened 30 Sept 2025. Intermittent closure based on trigger levels.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -674,25 +674,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/131536/faqs</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.6748</v>
+        <v>51.670535</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.2887</v>
+        <v>-1.269202</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -703,17 +703,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure</t>
+          <t>Temple Footbridge Closure</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Environment Agency closed for safety. Divert via Bisham Abbey and minor roads to Marlow</t>
+          <t>Closed May 2023. Structural concerns. Unlikely to reopen until 2028 at earliest. Diversion via Marlow Bridge.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -721,25 +721,29 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n"/>
+          <t>Active - long term closure</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.thamespath.org.uk/2025/12/04/temple-bridge-closed-until-2028-at-least/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.5222</v>
+        <v>51.565</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.8171</v>
+        <v>-0.8139999999999999</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -755,12 +759,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Runnymede Bridge 142 closure</t>
+          <t>Bridge 142 (Runnymede)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed, diversion via A308 pavements, extended to 2027</t>
+          <t>Footbridge closed Feb 2024 for structural damage. Diversion via A308/Causeway. Repairs unlikely until 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -768,13 +772,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n"/>
+          <t>Active - extended closure</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -783,16 +791,16 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.4298</v>
+        <v>51.433</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5431</v>
+        <v>-0.509</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -802,12 +810,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock refurbishment</t>
+          <t>Bell Weir Lock Diversion</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thames Path diverted at Runnymede Pleasure Ground during refurbishment works April 2026-Autumn 2027</t>
+          <t>Small diversion around compound at Runnymede Pleasure Grounds for Bell Weir refurbishment works.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -815,50 +823,46 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.4285</v>
+        <v>51.433</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.546</v>
+        <v>-0.529</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath diversion</t>
+          <t>Streatley-Goring Towpath Diversion</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Path reopened after resurfacing March 2026, previously diverted</t>
+          <t>Path narrow and floods frequently. Diversion via Footpath 227 and Manor Road.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -866,17 +870,13 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>reopened</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.6121</v>
+        <v>51.568</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.3076</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -899,17 +899,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure</t>
+          <t>Penton Hook Island Closure</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>No access to island due to diseased trees, Thames Path unaffected</t>
+          <t>Island closed due to diseased and dangerous trees. Thames Path unaffected but island access restricted.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -917,46 +917,42 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.4293</v>
+        <v>51.428</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.508</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>closure</t>
-        </is>
-      </c>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure</t>
+          <t>Ten Foot Bridge</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Structurally unsafe, closed March 2024, full specialist survey completed pending resolution</t>
+          <t>Wooden footbridge (not part of Thames Path). Path stays on same bank. Reported closed by walkers.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -964,29 +960,25 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
+          <t>https://www.alltrails.com/trail/england/oxfordshire/thames-path-tadpole-bridge-to-northmoor</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.7912</v>
+        <v>51.694</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.5715</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -997,17 +989,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal disruption</t>
+          <t>Brentford Grand Union Canal Disruption</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Left bank path blocked during redevelopment, parts now open via alternative routes through canal</t>
+          <t>Left bank Grand Union Canal blocked between River Brent bridge and Brentford Marina. Area redeveloped. Alternative route via High Street. Parts now reopened.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1015,13 +1007,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Partial reopening</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1030,61 +1022,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.4891</v>
+        <v>51.481</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.3081</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>closure</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Benson Weir walkway reopened</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Footbridge reopened April 1, 2026 after 3+ years closed for repairs, diversion removed</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>reopened</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>51.6161</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>-1.1389</v>
+        <v>-0.307</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -510,48 +510,48 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge Diversion</t>
+          <t>Marsh Lock Footbridge closure</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed 150 yards before bridge. Diversion via Abbey Road parallel to river.</t>
+          <t>Thames Path closed at Marsh Lock south of Henley-on-Thames. Diversion via A4155 approximately 3 miles. Environment Agency closed for safety grounds.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>53.8</v>
+        <v>105.1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Active - closure order until 31 Jan 2026, likely extended</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.752694</v>
+        <v>51.462</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.273093</v>
+        <v>-0.909</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -567,38 +567,38 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock Footbridge Closure</t>
+          <t>Temple Footbridge closed</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety. 3-mile diversion via A4155 pavements. Train/bus available.</t>
+          <t>Temple Footbridge permanently closed due to structural issues. Diversion via Marlow Bridge and Bisham Abbey to Marlow. Note: Marlow Bridge closed weekends 14/15 March, 11/12 April, 18/19 April.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>105.1</v>
+        <v>108.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Active - extends beyond Jan 2026</t>
+          <t>Active - closed indefinitely from May 2023</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.457</v>
+        <v>51.432</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.903</v>
+        <v>-0.839</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -614,12 +614,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge Closure</t>
+          <t>Sandford Footbridge closure</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge closed. Diversion via NCN Route 5.</t>
+          <t>Footbridge north of Sandford Lock closed for safety. Diversion via NCN 5 cycle route.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -627,13 +627,13 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Active - closed due to structural issues</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.662</v>
+        <v>51.678</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.179</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -661,12 +661,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir Walkway</t>
+          <t>Abingdon Weir walkway closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Closed when river levels high/fast. Reopened 30 Sept 2025. Intermittent closure based on trigger levels.</t>
+          <t>Walkway across Abingdon Weir closed due to corrosion. Path rerouted via Abingdon town centre. Reopens at low river levels, closes when levels rise.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -674,25 +674,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Intermittent - dependent on river level</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/131536/faqs</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.670535</v>
+        <v>51.667</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.269202</v>
+        <v>-1.301</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -703,47 +703,43 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge Closure</t>
+          <t>Osney Bridge diversion</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Closed May 2023. Structural concerns. Unlikely to reopen until 2028 at earliest. Diversion via Marlow Bridge.</t>
+          <t>Towpath closed about 150 yards from Osney Bridge. Diversion via Abbey Road and Botley Road to rejoin at bridge.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>108.5</v>
+        <v>53.8</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Active - long term closure</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
+          <t>Active - ongoing diversion</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/04/temple-bridge-closed-until-2028-at-least/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.565</v>
+        <v>51.752</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-1.273</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -759,39 +755,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 (Runnymede)</t>
+          <t>Bell Weir Lock site works diversion</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed Feb 2024 for structural damage. Diversion via A308/Causeway. Repairs unlikely until 2027.</t>
+          <t>Small diversion at Runnymede Pleasure Grounds around compound with standing machinery for Bell Weir refurbishment works. Spring 2026 to autumn 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>136.5</v>
+        <v>136.2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Active - extended closure</t>
+          <t>Active - construction ongoing through autumn 2027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.433</v>
+        <v>51.432</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>-0.509</v>
@@ -800,95 +796,95 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock Diversion</t>
+          <t>Runnymede Bridge 142 footbridge closure</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Small diversion around compound at Runnymede Pleasure Grounds for Bell Weir refurbishment works.</t>
+          <t>Footbridge south of Runnymede Bridge/M25 closed for public safety due to structural damage from flooding. Diversion via A308 and Causeway. Expected closure early 2024 to at least 2026.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>136.2</v>
+        <v>136.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Active - closure until at least 2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.433</v>
+        <v>51.429</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.529</v>
+        <v>-0.503</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring Towpath Diversion</t>
+          <t>Penton Hook Island closure</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Path narrow and floods frequently. Diversion via Footpath 227 and Manor Road.</t>
+          <t>Penton Hook Island closed to public due to diseased ash trees posing safety risk. Tree clearance work planned after bird nesting season (after September). Thames Path unaffected.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>81.5</v>
+        <v>135.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Active - closed since July 2025</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.568</v>
+        <v>51.444</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.16</v>
+        <v>-0.448</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -899,107 +895,115 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island Closure</t>
+          <t>Ten Foot Bridge closure</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island closed due to diseased and dangerous trees. Thames Path unaffected but island access restricted.</t>
+          <t>Ten Foot Bridge between Rushey and Shifford locks near Buckland village in Faringdon closed March 2024 due to structural and safety concerns. No reopening date confirmed.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>135.6</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
+          <t>Active - closed March 2024 indefinitely</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.428</v>
+        <v>51.693</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.508</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n"/>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>diversion</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge</t>
+          <t>Streatley-Goring towpath diversion</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Wooden footbridge (not part of Thames Path). Path stays on same bank. Reported closed by walkers.</t>
+          <t>Weir damaged in 2022 and being repaired. Diversion via minor roads through Preston Crowmarsh and Howbery Business Park, crossing at Wallingford Bridge. Shuttle ferry service available weekends 10am-4pm.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34</v>
+        <v>81.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Active - diversion in place, ferry service limited</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.alltrails.com/trail/england/oxfordshire/thames-path-tadpole-bridge-to-northmoor</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.694</v>
+        <v>51.472</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.49</v>
+        <v>-1.097</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal Disruption</t>
+          <t>Brentford Grand Union Canal disruption</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Left bank Grand Union Canal blocked between River Brent bridge and Brentford Marina. Area redeveloped. Alternative route via High Street. Parts now reopened.</t>
+          <t>Path blocked on left bank of Grand Union Canal between bridge over River Brent and Brentford Marina. Parts now open - possible to walk The Ham, cross canal, follow canal to Thames Lock, cross back at Lock and follow Dock Road.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1007,13 +1011,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Partial reopening</t>
+          <t>Partially reopened - partial access restored</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1022,7 +1026,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.481</v>
+        <v>51.493</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>-0.307</v>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -520,38 +520,38 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock Footbridge closure</t>
+          <t>Osney Bridge towpath closure Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Thames Path closed at Marsh Lock south of Henley-on-Thames. Diversion via A4155 approximately 3 miles. Environment Agency closed for safety grounds.</t>
+          <t>Towpath closed 150 yards upstream from bridge. Diversion via Abbey Road and Botley Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>105.1</v>
+        <v>53.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Active - closure order until 31 Jan 2026, likely extended</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.462</v>
+        <v>51.753</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.909</v>
+        <v>-1.273</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -567,38 +567,38 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closed</t>
+          <t>Marsh Lock Footbridge closure Henley</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge permanently closed due to structural issues. Diversion via Marlow Bridge and Bisham Abbey to Marlow. Note: Marlow Bridge closed weekends 14/15 March, 11/12 April, 18/19 April.</t>
+          <t>Footbridge closed for safety. 2.7-3 mile diversion via A4155 between Shiplake and Henley.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>108.5</v>
+        <v>105.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Active - closed indefinitely from May 2023</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.432</v>
+        <v>51.534</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.839</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -619,7 +619,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Footbridge north of Sandford Lock closed for safety. Diversion via NCN 5 cycle route.</t>
+          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -627,13 +627,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Active - closed due to structural issues</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -642,10 +646,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.678</v>
+        <v>51.681</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.267</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -661,12 +665,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway closure</t>
+          <t>Abingdon Weir walkway intermittent closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway across Abingdon Weir closed due to corrosion. Path rerouted via Abingdon town centre. Reopens at low river levels, closes when levels rise.</t>
+          <t>Corrosion damage. Closed intermittently during high water/high flows. Diverted via town centre.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -674,25 +678,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Intermittent - dependent on river level</t>
+          <t>active intermittent</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/abingdon-weir-walkway</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.667</v>
+        <v>51.671</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.301</v>
+        <v>-1.293</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -708,38 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge diversion</t>
+          <t>Temple Footbridge closure Hurley/Marlow</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed about 150 yards from Osney Bridge. Diversion via Abbey Road and Botley Road to rejoin at bridge.</t>
+          <t>Closed May 2023. Central span removed November 2025. Unlikely to reopen before 2028.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>53.8</v>
+        <v>108.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Active - ongoing diversion</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.752</v>
+        <v>51.552</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-1.273</v>
+        <v>-0.797</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -755,42 +763,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock site works diversion</t>
+          <t>Bridge 142 closure near Egham Runnymede</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Small diversion at Runnymede Pleasure Grounds around compound with standing machinery for Bell Weir refurbishment works. Spring 2026 to autumn 2027.</t>
+          <t>Tree strike damage Feb 2024. Structural closure. Diversion via A308. Expected to remain closed until 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>136.2</v>
+        <v>136.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Active - construction ongoing through autumn 2027</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.432</v>
+        <v>51.445</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.509</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -801,43 +809,43 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Runnymede Bridge 142 footbridge closure</t>
+          <t>Bell Weir Lock diversion Runnymede</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Footbridge south of Runnymede Bridge/M25 closed for public safety due to structural damage from flooding. Diversion via A308 and Causeway. Expected closure early 2024 to at least 2026.</t>
+          <t>Small diversion at Runnymede Pleasure Grounds for refurbishment works. Thames Path diverted around compound.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>136.5</v>
+        <v>136.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Active - closure until at least 2026</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.429</v>
+        <v>51.447</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.503</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -848,43 +856,43 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure</t>
+          <t>Streatley-Goring towpath diversion eroding path</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closed to public due to diseased ash trees posing safety risk. Tree clearance work planned after bird nesting season (after September). Thames Path unaffected.</t>
+          <t>0.5 mile diversion due to eroding towpath. Unlikely to reopen until late 2026.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135.6</v>
+        <v>81.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Active - closed since July 2025</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.444</v>
+        <v>51.522</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.448</v>
+        <v>-1.142</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -895,47 +903,47 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure</t>
+          <t>Penton Hook Island closure diseased trees</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge between Rushey and Shifford locks near Buckland village in Faringdon closed March 2024 due to structural and safety concerns. No reopening date confirmed.</t>
+          <t>Island closed due to diseased ash trees. Thames Path unaffected but island access denied.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34</v>
+        <v>135.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Active - closed March 2024 indefinitely</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.693</v>
+        <v>51.433</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-1.49</v>
+        <v>-0.442</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -946,64 +954,68 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath diversion</t>
+          <t>Ten Foot Bridge closure Faringdon</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Weir damaged in 2022 and being repaired. Diversion via minor roads through Preston Crowmarsh and Howbery Business Park, crossing at Wallingford Bridge. Shuttle ferry service available weekends 10am-4pm.</t>
+          <t>Structural safety concerns. Closed March 2024. No reopening date announced.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>81.5</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Active - diversion in place, ferry service limited</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.472</v>
+        <v>51.686</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.097</v>
+        <v>-1.494</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal disruption</t>
+          <t>Brentford Grand Union Canal left bank disruption</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between bridge over River Brent and Brentford Marina. Parts now open - possible to walk The Ham, cross canal, follow canal to Thames Lock, cross back at Lock and follow Dock Road.</t>
+          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Marina. Redevelopment ongoing.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1011,13 +1023,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Partially reopened - partial access restored</t>
+          <t>active partial</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1026,10 +1038,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.493</v>
+        <v>51.49</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.307</v>
+        <v>-0.305</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge towpath closure Oxford</t>
+          <t>Osney Bridge towpath diversion</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed 150 yards upstream from bridge. Diversion via Abbey Road and Botley Road.</t>
+          <t>Towpath closed 150 yards before bridge. Diversion along Abbey Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.753</v>
+        <v>51.752694</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.273</v>
+        <v>-1.273093</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -562,17 +562,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock Footbridge closure Henley</t>
+          <t>Marsh Lock footbridge closed Henley-Shiplake</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety. 2.7-3 mile diversion via A4155 between Shiplake and Henley.</t>
+          <t>Marsh Lock footbridge closed May 2022 for safety. 2.7 mile diversion via A4155. Closure extended beyond 31 Jan 2026.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -586,7 +586,7 @@
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.534</v>
+        <v>51.47</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.846</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -619,7 +619,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN5.</t>
+          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -630,14 +630,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -646,16 +642,16 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.681</v>
+        <v>51.716</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.228</v>
+        <v>-1.297</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>incident</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -670,7 +666,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Corrosion damage. Closed intermittently during high water/high flows. Diverted via town centre.</t>
+          <t>Weir walkway closed due to high water levels and corrosion. Intermittent closure reopened 30 Sept 2025. Diverts via Abingdon town centre.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -678,25 +674,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active intermittent</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/abingdon-weir-walkway</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/abingdon-weir-closure-april-2025/</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.671</v>
+        <v>51.67</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.293</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -712,12 +708,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure Hurley/Marlow</t>
+          <t>Temple Footbridge closed Marlow-Hurley</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Closed May 2023. Central span removed November 2025. Unlikely to reopen before 2028.</t>
+          <t>Temple Footbridge closed May 2023. Centre span removed Nov 2025. Unlikely to reopen until 2028. Diversion via Marlow Bridge.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -728,14 +724,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -744,10 +736,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.552</v>
+        <v>51.531</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.797</v>
+        <v>-0.827</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -763,12 +755,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 closure near Egham Runnymede</t>
+          <t>Bridge 142 closure near Runnymede M25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tree strike damage Feb 2024. Structural closure. Diversion via A308. Expected to remain closed until 2027.</t>
+          <t>Footbridge damaged Feb 2024 after tree strike. Diversion 0.6 mi via A308. Expected until 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -779,32 +771,28 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-01</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.445</v>
+        <v>51.439</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.532</v>
+        <v>-0.531</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>incident</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -814,12 +802,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion Runnymede</t>
+          <t>Bell Weir Lock construction diversion</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Small diversion at Runnymede Pleasure Grounds for refurbishment works. Thames Path diverted around compound.</t>
+          <t>Thames Path diverted at Runnymede Pleasure Ground due to Bell Weir refurbishment works. Small compound diversion. Work spring 2026 to autumn 2027.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -833,19 +821,19 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.447</v>
+        <v>51.444</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.527</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -856,21 +844,21 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath diversion eroding path</t>
+          <t>Penton Hook Island closure</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0.5 mile diversion due to eroding towpath. Unlikely to reopen until late 2026.</t>
+          <t>Penton Hook Island closed due to diseased trees (ash dieback). Path unaffected but island inaccessible. No reopening date.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>81.5</v>
+        <v>135.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -880,19 +868,19 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/penton-hook-island-temporary-closure</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.522</v>
+        <v>51.443</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.142</v>
+        <v>-0.515</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -908,93 +896,85 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure diseased trees</t>
+          <t>Ten Foot Bridge closure Faringdon</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island closed due to diseased ash trees. Thames Path unaffected but island access denied.</t>
+          <t>Ten Foot Bridge between Rushey and Shifford Locks near Buckland closed March 2024 for structural safety concerns. No reopening date.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>135.6</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.433</v>
+        <v>51.694</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.442</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>incident</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure Faringdon</t>
+          <t>Brentford Grand Union Canal disruption</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Structural safety concerns. Closed March 2024. No reopening date announced.</t>
+          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Area being redeveloped. Partial reopening reported.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34</v>
+        <v>154</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.686</v>
+        <v>51.487</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.494</v>
+        <v>-0.307</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -1010,38 +990,38 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal left bank disruption</t>
+          <t>Streatley-Goring towpath diversion</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Marina. Redevelopment ongoing.</t>
+          <t>Footpath south of Streatley/Goring closed for riverbank repairs. Diversion via Manor Road and Footpath 227. Riverside route unlikely to reopen until late 2026.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>154</v>
+        <v>81.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>active partial</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.49</v>
+        <v>51.558</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.305</v>
+        <v>-1.136</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -510,7 +510,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge towpath diversion</t>
+          <t>Osney Bridge diversion Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed 150 yards before bridge. Diversion along Abbey Road.</t>
+          <t>Towpath closed about 150 yards from bridge. Diversion via Abbey Road and Botley Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.752694</v>
+        <v>51.7527</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.273093</v>
+        <v>-1.2731</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -562,17 +562,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closed Henley-Shiplake</t>
+          <t>Marsh Lock Footbridge closure Henley</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closed May 2022 for safety. 2.7 mile diversion via A4155. Closure extended beyond 31 Jan 2026.</t>
+          <t>Footbridge closed for safety. 3-mile diversion via A4155 pavements between Henley and Shiplake. Order active until 31 January 2026 (likely extended).</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -586,7 +586,7 @@
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.47</v>
+        <v>51.4633</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.93</v>
+        <v>-0.9065</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -619,7 +619,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5.</t>
+          <t>Unsafe footbridge north (upstream) of Sandford Lock closed. Diversion via NCN 5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -633,7 +633,7 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.716</v>
+        <v>51.6667</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.297</v>
+        <v>-1.1667</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>incident</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weir walkway closed due to high water levels and corrosion. Intermittent closure reopened 30 Sept 2025. Diverts via Abingdon town centre.</t>
+          <t>Walkway closed due to corrosion. Rerouted via Abingdon town centre. Closes when river levels rise or weir gates operate.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -674,25 +674,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/abingdon-weir-closure-april-2025/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/131327/faqs</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.67</v>
+        <v>51.6333</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.29</v>
+        <v>-1.2833</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -708,12 +708,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closed Marlow-Hurley</t>
+          <t>Temple Footbridge closure Marlow</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closed May 2023. Centre span removed Nov 2025. Unlikely to reopen until 2028. Diversion via Marlow Bridge.</t>
+          <t>Closed May 2023 due to structural damage. Central span removed Nov 2025. Unlikely to reopen until 2028. Diversion via Marlow Bridge and Bisham.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -724,10 +724,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -736,10 +740,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.531</v>
+        <v>51.5611</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.827</v>
+        <v>-0.7344000000000001</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -755,12 +759,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 closure near Runnymede M25</t>
+          <t>Bridge 142 closure Egham</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Footbridge damaged Feb 2024 after tree strike. Diversion 0.6 mi via A308. Expected until 2027.</t>
+          <t>Footbridge closed Feb 2024 for safety. Structural damage. 0.6-mile diversion via A308 pavements.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -771,28 +775,32 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/131327/faqs</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.439</v>
+        <v>51.4333</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.531</v>
+        <v>-0.5283</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>incident</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -802,12 +810,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock construction diversion</t>
+          <t>Bell Weir Lock diversion Runnymede</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thames Path diverted at Runnymede Pleasure Ground due to Bell Weir refurbishment works. Small compound diversion. Work spring 2026 to autumn 2027.</t>
+          <t>Small diversion around construction compound at Runnymede Pleasure Ground for Bell Weir refurbishment works. Spring 2026 to autumn 2027.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -821,7 +829,7 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -830,35 +838,35 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.444</v>
+        <v>51.4339</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.527</v>
+        <v>-0.5194</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure</t>
+          <t>Streatley-Goring towpath diversion</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closed due to diseased trees (ash dieback). Path unaffected but island inaccessible. No reopening date.</t>
+          <t>0.5-mile diversion south of Streatley due to eroding towpath. Unlikely to reopen until late 2026.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135.6</v>
+        <v>81.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -868,44 +876,44 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/penton-hook-island-temporary-closure</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.443</v>
+        <v>51.5131</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.515</v>
+        <v>-1.1378</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>null</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure Faringdon</t>
+          <t>Penton Hook Island closure</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge between Rushey and Shifford Locks near Buckland closed March 2024 for structural safety concerns. No reopening date.</t>
+          <t>Island closed to public due to diseased trees (ash dieback). Thames Path itself unaffected.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34</v>
+        <v>135.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -915,91 +923,95 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.694</v>
+        <v>51.4217</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-1.49</v>
+        <v>-0.4556</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>incident</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal disruption</t>
+          <t>Ten Foot Bridge closure Faringdon</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Area being redeveloped. Partial reopening reported.</t>
+          <t>Closed March 2024 due to structural and safety concerns. Follow-up specialist survey completed.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>154</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.487</v>
+        <v>51.6942</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-0.307</v>
+        <v>-1.4899</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>incident</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>null</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath diversion</t>
+          <t>Brentford Grand Union Canal disruption</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Footpath south of Streatley/Goring closed for riverbank repairs. Diversion via Manor Road and Footpath 227. Riverside route unlikely to reopen until late 2026.</t>
+          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Area being redeveloped.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>81.5</v>
+        <v>154</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1009,19 +1021,19 @@
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.558</v>
+        <v>51.49</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-1.136</v>
+        <v>-0.2989</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed about 150 yards from bridge. Diversion via Abbey Road and Botley Road.</t>
+          <t>Towpath closed about 150 yards before bridge. Diversion via Abbey Road and Botley Road. Alternative continues via revised route.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock Footbridge closure Henley</t>
+          <t>Marsh Lock Henley footbridge closure</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety. 3-mile diversion via A4155 pavements between Henley and Shiplake. Order active until 31 January 2026 (likely extended).</t>
+          <t>Closed for safety since May 2022. 3-mile diversion via A4155 pavements. No through access until further notice. Expected to remain until 31 January 2026, may be extended.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -580,13 +580,17 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,10 +599,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.4633</v>
+        <v>51.4833</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.9065</v>
+        <v>-0.7333</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -619,7 +623,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north (upstream) of Sandford Lock closed. Diversion via NCN 5.</t>
+          <t>Unsafe footbridge north of Sandford Lock closed April 2025. Diversion via NCN 5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -627,13 +631,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -642,10 +650,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.6667</v>
+        <v>51.6833</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.1667</v>
+        <v>-1.2333</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -666,7 +674,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway closed due to corrosion. Rerouted via Abingdon town centre. Closes when river levels rise or weir gates operate.</t>
+          <t>Due to corrosion, walkway closed and re-routed via Abingdon town centre. Closes during high river levels and high flows, reopens when levels recede.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -680,19 +688,19 @@
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/131327/faqs</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.6333</v>
+        <v>51.6702</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.2833</v>
+        <v>-1.2693</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -703,17 +711,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure Marlow</t>
+          <t>Temple Footbridge closure near Marlow</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Closed May 2023 due to structural damage. Central span removed Nov 2025. Unlikely to reopen until 2028. Diversion via Marlow Bridge and Bisham.</t>
+          <t>Closed since May 2023 for safety. Central span removed November 2025, beyond economical repair. Unlikely to reopen until 2028 at earliest.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -721,7 +729,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -731,7 +739,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -740,10 +748,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.5611</v>
+        <v>51.552</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.797</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -759,12 +767,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 closure Egham</t>
+          <t>Bridge 142 Runnymede closure Egham</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed Feb 2024 for safety. Structural damage. 0.6-mile diversion via A308 pavements.</t>
+          <t>Closed February 2024 due to structural damage from flooding. Diversion via A308/Runnymede Hotel area. Expected until at least 2026, possibly 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -772,7 +780,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -782,25 +790,25 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/131327/faqs</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.4333</v>
+        <v>51.4375</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5283</v>
+        <v>-0.5347</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -810,12 +818,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion Runnymede</t>
+          <t>Bell Weir Lock refurbishment diversion</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Small diversion around construction compound at Runnymede Pleasure Ground for Bell Weir refurbishment works. Spring 2026 to autumn 2027.</t>
+          <t>Temporary diversion at Runnymede Pleasure Ground due to Bell Weir refurbishment works. Work started spring 2026, planned completion autumn 2027.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -826,10 +834,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -838,10 +850,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.4339</v>
+        <v>51.4301</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.5194</v>
+        <v>-0.5347</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -862,7 +874,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0.5-mile diversion south of Streatley due to eroding towpath. Unlikely to reopen until late 2026.</t>
+          <t>Half-mile diversion south of Goring Bridge due to eroding towpath. Funding insufficient for repairs. Unlikely to reopen until late 2026 at earliest.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -876,19 +888,19 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.5131</v>
+        <v>51.5229</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.1378</v>
+        <v>-1.1425</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -909,7 +921,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island closed to public due to diseased trees (ash dieback). Thames Path itself unaffected.</t>
+          <t>Island closed to public due to diseased trees (ash dieback). Thames Path unaffected. Complex clearance work ongoing.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -917,13 +929,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -932,10 +948,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.4217</v>
+        <v>51.4412</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.4556</v>
+        <v>-0.5185999999999999</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -956,7 +972,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Closed March 2024 due to structural and safety concerns. Follow-up specialist survey completed.</t>
+          <t>Closed March 2024 due to structural concerns. Between Rushey and Shifford locks near Buckland. Specialist survey completed but reopening date uncertain.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -964,7 +980,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -974,7 +990,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1007,7 +1023,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between River Brent bridge and Brentford Marina. Area being redeveloped.</t>
+          <t>Left bank blocked between River Brent bridge and Brentford Marina. No official diversion. Area being redeveloped. Some sections now open.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1015,13 +1031,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1030,10 +1046,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.49</v>
+        <v>51.4903</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.2989</v>
+        <v>-0.3027</v>
       </c>
     </row>
   </sheetData>
